--- a/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
+++ b/test_data/Orion_Stress_Demo/PN-BETA-02/40202/BU07/HRM/post DFS_HRM-2031-0460/Panel 7/Coupon-Front/2031-03-01_08-00-00_ENG_Orion_Stress_Demo_BU07_Coupon_Front_Summary.xlsx
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>17.53534</v>
+        <v>17.29294</v>
       </c>
       <c r="D2" t="n">
-        <v>16.98296</v>
+        <v>16.81193</v>
       </c>
       <c r="E2" t="n">
-        <v>17.42605</v>
+        <v>17.23401</v>
       </c>
       <c r="F2" t="n">
-        <v>43.67175</v>
+        <v>43.34752</v>
       </c>
       <c r="G2" t="n">
-        <v>0.05278</v>
+        <v>0.05194</v>
       </c>
       <c r="H2" t="n">
-        <v>1.84592</v>
+        <v>1.84538</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>17.20499</v>
+        <v>17.49159</v>
       </c>
       <c r="D3" t="n">
-        <v>17.17373</v>
+        <v>16.97023</v>
       </c>
       <c r="E3" t="n">
-        <v>16.8618</v>
+        <v>17.48579</v>
       </c>
       <c r="F3" t="n">
-        <v>43.8943</v>
+        <v>43.97928</v>
       </c>
       <c r="G3" t="n">
-        <v>0.05181</v>
+        <v>0.05216</v>
       </c>
       <c r="H3" t="n">
-        <v>1.91299</v>
+        <v>1.88826</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>17.49629</v>
+        <v>17.24774</v>
       </c>
       <c r="D4" t="n">
-        <v>16.97572</v>
+        <v>16.81213</v>
       </c>
       <c r="E4" t="n">
-        <v>17.25037</v>
+        <v>17.07649</v>
       </c>
       <c r="F4" t="n">
-        <v>43.61877</v>
+        <v>43.51757</v>
       </c>
       <c r="G4" t="n">
-        <v>0.05158</v>
+        <v>0.05246</v>
       </c>
       <c r="H4" t="n">
-        <v>1.88159</v>
+        <v>1.91149</v>
       </c>
     </row>
     <row r="5">
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.1093</v>
+        <v>16.89505</v>
       </c>
       <c r="D6" t="n">
-        <v>16.75566</v>
+        <v>16.56497</v>
       </c>
       <c r="E6" t="n">
-        <v>16.88691</v>
+        <v>16.71977</v>
       </c>
       <c r="F6" t="n">
-        <v>22.69102</v>
+        <v>22.13852</v>
       </c>
       <c r="G6" t="n">
-        <v>35.25962</v>
+        <v>35.61159</v>
       </c>
     </row>
     <row r="7">
@@ -589,19 +589,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>17.3695</v>
+        <v>16.94818</v>
       </c>
       <c r="D7" t="n">
-        <v>16.07929</v>
+        <v>16.5223</v>
       </c>
       <c r="E7" t="n">
-        <v>16.84519</v>
+        <v>16.61776</v>
       </c>
       <c r="F7" t="n">
-        <v>22.34965</v>
+        <v>22.66185</v>
       </c>
       <c r="G7" t="n">
-        <v>35.56199</v>
+        <v>35.18777</v>
       </c>
     </row>
     <row r="8">
@@ -611,19 +611,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>17.35033</v>
+        <v>17.63644</v>
       </c>
       <c r="D8" t="n">
-        <v>16.82263</v>
+        <v>16.57299</v>
       </c>
       <c r="E8" t="n">
-        <v>16.6801</v>
+        <v>17.12529</v>
       </c>
       <c r="F8" t="n">
-        <v>22.51891</v>
+        <v>22.46684</v>
       </c>
       <c r="G8" t="n">
-        <v>34.45529</v>
+        <v>35.334</v>
       </c>
     </row>
     <row r="9">
@@ -650,10 +650,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.61676</v>
+        <v>0.6191</v>
       </c>
       <c r="D10" t="n">
-        <v>1.15578</v>
+        <v>1.15311</v>
       </c>
     </row>
     <row r="11">
@@ -663,10 +663,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.6189</v>
+        <v>0.61958</v>
       </c>
       <c r="D11" t="n">
-        <v>1.14853</v>
+        <v>1.11631</v>
       </c>
     </row>
     <row r="12">
@@ -676,10 +676,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.6299</v>
+        <v>0.62738</v>
       </c>
       <c r="D12" t="n">
-        <v>1.15875</v>
+        <v>1.15767</v>
       </c>
     </row>
   </sheetData>
